--- a/datasets/sample_data/staff.xlsx
+++ b/datasets/sample_data/staff.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="421">
   <si>
     <t>Staff_ID</t>
   </si>
@@ -265,336 +265,342 @@
     <t>STF1068</t>
   </si>
   <si>
-    <t>Ffion</t>
+    <t>Patricia</t>
+  </si>
+  <si>
+    <t>Jennifer</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Megan</t>
+  </si>
+  <si>
+    <t>Susan</t>
+  </si>
+  <si>
+    <t>Emyr</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Linda</t>
+  </si>
+  <si>
+    <t>Aled</t>
+  </si>
+  <si>
+    <t>Dafydd</t>
+  </si>
+  <si>
+    <t>Owen</t>
+  </si>
+  <si>
+    <t>Iwan</t>
+  </si>
+  <si>
+    <t>Dylan</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Barbara</t>
+  </si>
+  <si>
+    <t>Angharad</t>
+  </si>
+  <si>
+    <t>Sian</t>
+  </si>
+  <si>
+    <t>Huw</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Elin</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>Gareth</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
+    <t>Rhys</t>
+  </si>
+  <si>
+    <t>Catrin</t>
   </si>
   <si>
     <t>Thomas</t>
   </si>
   <si>
-    <t>Sian</t>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Gwen</t>
   </si>
   <si>
     <t>Carys</t>
   </si>
   <si>
-    <t>Dafydd</t>
-  </si>
-  <si>
-    <t>Gareth</t>
-  </si>
-  <si>
-    <t>Susan</t>
-  </si>
-  <si>
-    <t>Margaret</t>
-  </si>
-  <si>
-    <t>William</t>
-  </si>
-  <si>
-    <t>Rhys</t>
-  </si>
-  <si>
-    <t>Robert</t>
-  </si>
-  <si>
-    <t>Elin</t>
-  </si>
-  <si>
-    <t>Owen</t>
-  </si>
-  <si>
-    <t>Helen</t>
-  </si>
-  <si>
-    <t>Jennifer</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Richard</t>
-  </si>
-  <si>
-    <t>Catrin</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>Karen</t>
-  </si>
-  <si>
-    <t>Iwan</t>
-  </si>
-  <si>
-    <t>Huw</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Gwen</t>
-  </si>
-  <si>
-    <t>Megan</t>
-  </si>
-  <si>
-    <t>Dylan</t>
+    <t>Rees</t>
+  </si>
+  <si>
+    <t>Griffiths</t>
+  </si>
+  <si>
+    <t>Powell</t>
+  </si>
+  <si>
+    <t>Lewis</t>
+  </si>
+  <si>
+    <t>Lloyd</t>
+  </si>
+  <si>
+    <t>Evans</t>
+  </si>
+  <si>
+    <t>Morris</t>
+  </si>
+  <si>
+    <t>Phillips</t>
   </si>
   <si>
     <t>James</t>
   </si>
   <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>Sarah</t>
-  </si>
-  <si>
-    <t>Phillips</t>
-  </si>
-  <si>
     <t>Jones</t>
   </si>
   <si>
     <t>Morgan</t>
   </si>
   <si>
-    <t>Lewis</t>
-  </si>
-  <si>
-    <t>Williams</t>
-  </si>
-  <si>
-    <t>Griffiths</t>
-  </si>
-  <si>
-    <t>Lloyd</t>
-  </si>
-  <si>
-    <t>Morris</t>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Roberts</t>
+  </si>
+  <si>
+    <t>Jenkins</t>
   </si>
   <si>
     <t>Hughes</t>
   </si>
   <si>
-    <t>Powell</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Roberts</t>
+    <t>Davies</t>
   </si>
   <si>
     <t>Edwards</t>
   </si>
   <si>
-    <t>Davies</t>
-  </si>
-  <si>
-    <t>Rees</t>
-  </si>
-  <si>
-    <t>Jenkins</t>
-  </si>
-  <si>
-    <t>Evans</t>
-  </si>
-  <si>
-    <t>Ffion Owen</t>
-  </si>
-  <si>
-    <t>Thomas Phillips</t>
-  </si>
-  <si>
-    <t>Sian Jones</t>
+    <t>Patricia Rees</t>
+  </si>
+  <si>
+    <t>Jennifer Griffiths</t>
+  </si>
+  <si>
+    <t>Mark Powell</t>
+  </si>
+  <si>
+    <t>Megan Owen</t>
+  </si>
+  <si>
+    <t>Jennifer Lewis</t>
+  </si>
+  <si>
+    <t>Jennifer Lloyd</t>
+  </si>
+  <si>
+    <t>Susan Powell</t>
+  </si>
+  <si>
+    <t>Emyr Evans</t>
+  </si>
+  <si>
+    <t>David Morris</t>
+  </si>
+  <si>
+    <t>Linda Phillips</t>
+  </si>
+  <si>
+    <t>Jennifer Evans</t>
+  </si>
+  <si>
+    <t>Aled Powell</t>
+  </si>
+  <si>
+    <t>Dafydd Owen</t>
+  </si>
+  <si>
+    <t>Owen James</t>
+  </si>
+  <si>
+    <t>Jennifer Owen</t>
+  </si>
+  <si>
+    <t>Iwan Jones</t>
+  </si>
+  <si>
+    <t>Dylan Lloyd</t>
+  </si>
+  <si>
+    <t>Sarah Morgan</t>
+  </si>
+  <si>
+    <t>Paul Evans</t>
+  </si>
+  <si>
+    <t>Barbara Price</t>
+  </si>
+  <si>
+    <t>Angharad Morgan</t>
+  </si>
+  <si>
+    <t>Megan Roberts</t>
+  </si>
+  <si>
+    <t>Owen Owen</t>
+  </si>
+  <si>
+    <t>Sian Phillips</t>
+  </si>
+  <si>
+    <t>Huw Evans</t>
+  </si>
+  <si>
+    <t>Richard Price</t>
+  </si>
+  <si>
+    <t>Dylan Jenkins</t>
+  </si>
+  <si>
+    <t>Elin Morgan</t>
+  </si>
+  <si>
+    <t>William Morgan</t>
+  </si>
+  <si>
+    <t>Paul Price</t>
+  </si>
+  <si>
+    <t>Owen Price</t>
+  </si>
+  <si>
+    <t>Paul Morris</t>
+  </si>
+  <si>
+    <t>Gareth Hughes</t>
+  </si>
+  <si>
+    <t>Sarah Powell</t>
+  </si>
+  <si>
+    <t>Gareth Morris</t>
+  </si>
+  <si>
+    <t>Huw Morris</t>
+  </si>
+  <si>
+    <t>Barbara Griffiths</t>
+  </si>
+  <si>
+    <t>Elizabeth Evans</t>
+  </si>
+  <si>
+    <t>Susan Jenkins</t>
+  </si>
+  <si>
+    <t>Richard Owen</t>
+  </si>
+  <si>
+    <t>Iwan Davies</t>
+  </si>
+  <si>
+    <t>Rhys Griffiths</t>
+  </si>
+  <si>
+    <t>David Jenkins</t>
+  </si>
+  <si>
+    <t>Elin Davies</t>
+  </si>
+  <si>
+    <t>Aled Rees</t>
+  </si>
+  <si>
+    <t>Sarah Price</t>
+  </si>
+  <si>
+    <t>Catrin Jones</t>
+  </si>
+  <si>
+    <t>David Jones</t>
+  </si>
+  <si>
+    <t>Megan Jones</t>
+  </si>
+  <si>
+    <t>Elizabeth James</t>
+  </si>
+  <si>
+    <t>Thomas Powell</t>
+  </si>
+  <si>
+    <t>John Rees</t>
+  </si>
+  <si>
+    <t>Gareth Edwards</t>
+  </si>
+  <si>
+    <t>Angharad Price</t>
+  </si>
+  <si>
+    <t>Iwan Lewis</t>
+  </si>
+  <si>
+    <t>Gwen Rees</t>
+  </si>
+  <si>
+    <t>Mark Griffiths</t>
+  </si>
+  <si>
+    <t>Carys Edwards</t>
+  </si>
+  <si>
+    <t>Iwan Morgan</t>
+  </si>
+  <si>
+    <t>Jennifer Davies</t>
+  </si>
+  <si>
+    <t>Huw Jenkins</t>
+  </si>
+  <si>
+    <t>Aled Price</t>
+  </si>
+  <si>
+    <t>Gwen Jones</t>
+  </si>
+  <si>
+    <t>Paul Roberts</t>
   </si>
   <si>
     <t>Carys Morgan</t>
   </si>
   <si>
-    <t>Sian James</t>
-  </si>
-  <si>
-    <t>Dafydd Jones</t>
-  </si>
-  <si>
-    <t>Gareth Lewis</t>
-  </si>
-  <si>
-    <t>Susan Williams</t>
-  </si>
-  <si>
-    <t>Margaret Morgan</t>
-  </si>
-  <si>
-    <t>William Griffiths</t>
-  </si>
-  <si>
-    <t>William Owen</t>
-  </si>
-  <si>
-    <t>Margaret Lewis</t>
-  </si>
-  <si>
-    <t>Rhys Lloyd</t>
-  </si>
-  <si>
-    <t>William Morris</t>
-  </si>
-  <si>
-    <t>Robert Lloyd</t>
-  </si>
-  <si>
-    <t>William Jones</t>
-  </si>
-  <si>
-    <t>Elin Jones</t>
-  </si>
-  <si>
-    <t>Owen Jones</t>
-  </si>
-  <si>
-    <t>Helen Thomas</t>
-  </si>
-  <si>
-    <t>Jennifer Hughes</t>
-  </si>
-  <si>
-    <t>Ffion Morgan</t>
-  </si>
-  <si>
-    <t>Mark Hughes</t>
-  </si>
-  <si>
-    <t>Sian Morris</t>
-  </si>
-  <si>
-    <t>Elizabeth Lloyd</t>
-  </si>
-  <si>
-    <t>David Owen</t>
-  </si>
-  <si>
-    <t>Richard Powell</t>
-  </si>
-  <si>
-    <t>Robert Griffiths</t>
-  </si>
-  <si>
-    <t>Catrin Price</t>
-  </si>
-  <si>
-    <t>Michael Roberts</t>
-  </si>
-  <si>
-    <t>Karen Griffiths</t>
-  </si>
-  <si>
-    <t>Robert Edwards</t>
-  </si>
-  <si>
-    <t>Robert Davies</t>
-  </si>
-  <si>
-    <t>Catrin Thomas</t>
-  </si>
-  <si>
-    <t>Thomas Hughes</t>
-  </si>
-  <si>
-    <t>Iwan Powell</t>
-  </si>
-  <si>
-    <t>Huw Thomas</t>
-  </si>
-  <si>
-    <t>John Jones</t>
-  </si>
-  <si>
-    <t>Rhys Griffiths</t>
-  </si>
-  <si>
-    <t>Margaret Phillips</t>
-  </si>
-  <si>
-    <t>Gwen Roberts</t>
-  </si>
-  <si>
-    <t>Megan Thomas</t>
-  </si>
-  <si>
-    <t>Catrin Lloyd</t>
-  </si>
-  <si>
-    <t>Elin Phillips</t>
-  </si>
-  <si>
-    <t>Dafydd Morris</t>
-  </si>
-  <si>
-    <t>Dylan Rees</t>
-  </si>
-  <si>
-    <t>Carys Lewis</t>
-  </si>
-  <si>
-    <t>Elin Edwards</t>
-  </si>
-  <si>
-    <t>James Griffiths</t>
-  </si>
-  <si>
-    <t>Paul Owen</t>
-  </si>
-  <si>
-    <t>Margaret Davies</t>
-  </si>
-  <si>
-    <t>Gwen Price</t>
-  </si>
-  <si>
-    <t>Sarah Thomas</t>
-  </si>
-  <si>
-    <t>Susan Lewis</t>
-  </si>
-  <si>
-    <t>Richard Rees</t>
-  </si>
-  <si>
-    <t>Huw Morris</t>
-  </si>
-  <si>
-    <t>Paul Morris</t>
-  </si>
-  <si>
-    <t>Richard Edwards</t>
-  </si>
-  <si>
-    <t>William Jenkins</t>
-  </si>
-  <si>
-    <t>Jennifer Williams</t>
-  </si>
-  <si>
-    <t>Dafydd Evans</t>
-  </si>
-  <si>
-    <t>Huw Edwards</t>
-  </si>
-  <si>
-    <t>James Edwards</t>
-  </si>
-  <si>
     <t>SACT Nurse</t>
   </si>
   <si>
@@ -649,18 +655,18 @@
     <t>Band 4</t>
   </si>
   <si>
+    <t>POW</t>
+  </si>
+  <si>
+    <t>WC</t>
+  </si>
+  <si>
+    <t>RGH</t>
+  </si>
+  <si>
     <t>CWM</t>
   </si>
   <si>
-    <t>RGH</t>
-  </si>
-  <si>
-    <t>WC</t>
-  </si>
-  <si>
-    <t>POW</t>
-  </si>
-  <si>
     <t>PCH</t>
   </si>
   <si>
@@ -868,412 +874,409 @@
     <t>staff1068@velindre.nhs.wales</t>
   </si>
   <si>
-    <t>9162</t>
-  </si>
-  <si>
-    <t>8057</t>
-  </si>
-  <si>
-    <t>4312</t>
-  </si>
-  <si>
-    <t>5000</t>
-  </si>
-  <si>
-    <t>9990</t>
-  </si>
-  <si>
-    <t>9277</t>
-  </si>
-  <si>
-    <t>6035</t>
-  </si>
-  <si>
-    <t>8605</t>
-  </si>
-  <si>
-    <t>5752</t>
-  </si>
-  <si>
-    <t>4635</t>
-  </si>
-  <si>
-    <t>6197</t>
-  </si>
-  <si>
-    <t>9901</t>
-  </si>
-  <si>
-    <t>1719</t>
-  </si>
-  <si>
-    <t>7746</t>
-  </si>
-  <si>
-    <t>7716</t>
-  </si>
-  <si>
-    <t>1183</t>
-  </si>
-  <si>
-    <t>5025</t>
-  </si>
-  <si>
-    <t>8111</t>
-  </si>
-  <si>
-    <t>5393</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>9533</t>
-  </si>
-  <si>
-    <t>3733</t>
-  </si>
-  <si>
-    <t>6312</t>
-  </si>
-  <si>
-    <t>8020</t>
-  </si>
-  <si>
-    <t>9472</t>
-  </si>
-  <si>
-    <t>3047</t>
-  </si>
-  <si>
-    <t>5256</t>
-  </si>
-  <si>
-    <t>9400</t>
-  </si>
-  <si>
-    <t>5198</t>
-  </si>
-  <si>
-    <t>2488</t>
-  </si>
-  <si>
-    <t>6937</t>
-  </si>
-  <si>
-    <t>7309</t>
-  </si>
-  <si>
-    <t>3971</t>
-  </si>
-  <si>
-    <t>3864</t>
-  </si>
-  <si>
-    <t>8677</t>
-  </si>
-  <si>
-    <t>7445</t>
-  </si>
-  <si>
-    <t>6233</t>
-  </si>
-  <si>
-    <t>2715</t>
-  </si>
-  <si>
-    <t>7694</t>
-  </si>
-  <si>
-    <t>9971</t>
-  </si>
-  <si>
-    <t>4404</t>
-  </si>
-  <si>
-    <t>8155</t>
-  </si>
-  <si>
-    <t>2536</t>
-  </si>
-  <si>
-    <t>3512</t>
-  </si>
-  <si>
-    <t>5861</t>
-  </si>
-  <si>
-    <t>8101</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>9908</t>
-  </si>
-  <si>
-    <t>2383</t>
-  </si>
-  <si>
-    <t>4156</t>
-  </si>
-  <si>
-    <t>6543</t>
-  </si>
-  <si>
-    <t>4837</t>
-  </si>
-  <si>
-    <t>1214</t>
-  </si>
-  <si>
-    <t>8428</t>
-  </si>
-  <si>
-    <t>1474</t>
-  </si>
-  <si>
-    <t>8963</t>
-  </si>
-  <si>
-    <t>3774</t>
-  </si>
-  <si>
-    <t>2545</t>
-  </si>
-  <si>
-    <t>9829</t>
-  </si>
-  <si>
-    <t>5538</t>
-  </si>
-  <si>
-    <t>4854</t>
-  </si>
-  <si>
-    <t>6829</t>
-  </si>
-  <si>
-    <t>2793</t>
-  </si>
-  <si>
-    <t>2454</t>
-  </si>
-  <si>
-    <t>6915</t>
-  </si>
-  <si>
-    <t>7757</t>
-  </si>
-  <si>
-    <t>3130</t>
-  </si>
-  <si>
-    <t>2577</t>
-  </si>
-  <si>
-    <t>2025-10-21</t>
-  </si>
-  <si>
-    <t>2020-06-12</t>
-  </si>
-  <si>
-    <t>2023-04-29</t>
-  </si>
-  <si>
-    <t>2025-03-22</t>
-  </si>
-  <si>
-    <t>2025-07-28</t>
-  </si>
-  <si>
-    <t>2017-05-18</t>
-  </si>
-  <si>
-    <t>2023-02-14</t>
-  </si>
-  <si>
-    <t>2020-11-25</t>
-  </si>
-  <si>
-    <t>2022-04-20</t>
-  </si>
-  <si>
-    <t>2022-09-04</t>
-  </si>
-  <si>
-    <t>2018-04-16</t>
-  </si>
-  <si>
-    <t>2016-10-24</t>
-  </si>
-  <si>
-    <t>2022-08-19</t>
-  </si>
-  <si>
-    <t>2021-08-12</t>
-  </si>
-  <si>
-    <t>2023-03-12</t>
-  </si>
-  <si>
-    <t>2016-05-11</t>
+    <t>4914</t>
+  </si>
+  <si>
+    <t>3258</t>
+  </si>
+  <si>
+    <t>6145</t>
+  </si>
+  <si>
+    <t>7882</t>
+  </si>
+  <si>
+    <t>1586</t>
+  </si>
+  <si>
+    <t>5277</t>
+  </si>
+  <si>
+    <t>7134</t>
+  </si>
+  <si>
+    <t>3035</t>
+  </si>
+  <si>
+    <t>6668</t>
+  </si>
+  <si>
+    <t>9365</t>
+  </si>
+  <si>
+    <t>9233</t>
+  </si>
+  <si>
+    <t>1640</t>
+  </si>
+  <si>
+    <t>2376</t>
+  </si>
+  <si>
+    <t>3232</t>
+  </si>
+  <si>
+    <t>4359</t>
+  </si>
+  <si>
+    <t>1589</t>
+  </si>
+  <si>
+    <t>9017</t>
+  </si>
+  <si>
+    <t>4298</t>
+  </si>
+  <si>
+    <t>5584</t>
+  </si>
+  <si>
+    <t>2179</t>
+  </si>
+  <si>
+    <t>3946</t>
+  </si>
+  <si>
+    <t>6974</t>
+  </si>
+  <si>
+    <t>2982</t>
+  </si>
+  <si>
+    <t>8735</t>
+  </si>
+  <si>
+    <t>6189</t>
+  </si>
+  <si>
+    <t>6975</t>
+  </si>
+  <si>
+    <t>8746</t>
+  </si>
+  <si>
+    <t>5211</t>
+  </si>
+  <si>
+    <t>2160</t>
+  </si>
+  <si>
+    <t>2813</t>
+  </si>
+  <si>
+    <t>3404</t>
+  </si>
+  <si>
+    <t>6394</t>
+  </si>
+  <si>
+    <t>8960</t>
+  </si>
+  <si>
+    <t>5063</t>
+  </si>
+  <si>
+    <t>3160</t>
+  </si>
+  <si>
+    <t>5542</t>
+  </si>
+  <si>
+    <t>9967</t>
+  </si>
+  <si>
+    <t>4362</t>
+  </si>
+  <si>
+    <t>5217</t>
+  </si>
+  <si>
+    <t>2864</t>
+  </si>
+  <si>
+    <t>8916</t>
+  </si>
+  <si>
+    <t>3687</t>
+  </si>
+  <si>
+    <t>3990</t>
+  </si>
+  <si>
+    <t>3057</t>
+  </si>
+  <si>
+    <t>3700</t>
+  </si>
+  <si>
+    <t>7789</t>
+  </si>
+  <si>
+    <t>2057</t>
+  </si>
+  <si>
+    <t>8380</t>
+  </si>
+  <si>
+    <t>7115</t>
+  </si>
+  <si>
+    <t>2877</t>
+  </si>
+  <si>
+    <t>2569</t>
+  </si>
+  <si>
+    <t>2402</t>
+  </si>
+  <si>
+    <t>7209</t>
+  </si>
+  <si>
+    <t>3111</t>
+  </si>
+  <si>
+    <t>8956</t>
+  </si>
+  <si>
+    <t>4779</t>
+  </si>
+  <si>
+    <t>1963</t>
+  </si>
+  <si>
+    <t>3668</t>
+  </si>
+  <si>
+    <t>7807</t>
+  </si>
+  <si>
+    <t>5479</t>
+  </si>
+  <si>
+    <t>4090</t>
+  </si>
+  <si>
+    <t>1372</t>
+  </si>
+  <si>
+    <t>6561</t>
+  </si>
+  <si>
+    <t>4514</t>
+  </si>
+  <si>
+    <t>7631</t>
+  </si>
+  <si>
+    <t>3581</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>4010</t>
+  </si>
+  <si>
+    <t>2019-05-07</t>
+  </si>
+  <si>
+    <t>2024-12-17</t>
+  </si>
+  <si>
+    <t>2019-06-08</t>
+  </si>
+  <si>
+    <t>2019-08-21</t>
+  </si>
+  <si>
+    <t>2017-08-04</t>
+  </si>
+  <si>
+    <t>2021-02-19</t>
+  </si>
+  <si>
+    <t>2019-05-05</t>
+  </si>
+  <si>
+    <t>2017-03-10</t>
+  </si>
+  <si>
+    <t>2022-01-01</t>
+  </si>
+  <si>
+    <t>2025-12-09</t>
+  </si>
+  <si>
+    <t>2019-08-18</t>
+  </si>
+  <si>
+    <t>2025-02-24</t>
+  </si>
+  <si>
+    <t>2016-08-28</t>
+  </si>
+  <si>
+    <t>2019-11-14</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>2016-09-29</t>
+  </si>
+  <si>
+    <t>2023-06-17</t>
+  </si>
+  <si>
+    <t>2019-10-26</t>
+  </si>
+  <si>
+    <t>2016-07-09</t>
+  </si>
+  <si>
+    <t>2019-08-16</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>2022-11-27</t>
+  </si>
+  <si>
+    <t>2023-06-08</t>
+  </si>
+  <si>
+    <t>2021-05-02</t>
+  </si>
+  <si>
+    <t>2025-07-14</t>
+  </si>
+  <si>
+    <t>2025-01-25</t>
+  </si>
+  <si>
+    <t>2019-07-10</t>
+  </si>
+  <si>
+    <t>2023-09-07</t>
+  </si>
+  <si>
+    <t>2020-05-20</t>
+  </si>
+  <si>
+    <t>2024-05-19</t>
+  </si>
+  <si>
+    <t>2018-07-19</t>
+  </si>
+  <si>
+    <t>2018-11-08</t>
+  </si>
+  <si>
+    <t>2016-04-30</t>
+  </si>
+  <si>
+    <t>2020-02-23</t>
+  </si>
+  <si>
+    <t>2016-05-22</t>
+  </si>
+  <si>
+    <t>2018-10-08</t>
+  </si>
+  <si>
+    <t>2017-04-06</t>
+  </si>
+  <si>
+    <t>2017-02-07</t>
+  </si>
+  <si>
+    <t>2024-08-01</t>
+  </si>
+  <si>
+    <t>2023-10-20</t>
+  </si>
+  <si>
+    <t>2018-08-05</t>
+  </si>
+  <si>
+    <t>2020-08-25</t>
+  </si>
+  <si>
+    <t>2023-09-10</t>
+  </si>
+  <si>
+    <t>2021-12-06</t>
+  </si>
+  <si>
+    <t>2022-08-23</t>
+  </si>
+  <si>
+    <t>2017-04-23</t>
+  </si>
+  <si>
+    <t>2019-02-02</t>
+  </si>
+  <si>
+    <t>2022-05-31</t>
+  </si>
+  <si>
+    <t>2023-04-09</t>
+  </si>
+  <si>
+    <t>2021-04-01</t>
+  </si>
+  <si>
+    <t>2017-04-16</t>
+  </si>
+  <si>
+    <t>2022-10-19</t>
   </si>
   <si>
     <t>2020-12-19</t>
   </si>
   <si>
-    <t>2019-01-08</t>
-  </si>
-  <si>
-    <t>2019-06-28</t>
-  </si>
-  <si>
-    <t>2023-08-05</t>
-  </si>
-  <si>
-    <t>2024-02-05</t>
-  </si>
-  <si>
-    <t>2020-01-12</t>
-  </si>
-  <si>
-    <t>2025-03-28</t>
-  </si>
-  <si>
-    <t>2022-07-12</t>
-  </si>
-  <si>
-    <t>2018-05-12</t>
-  </si>
-  <si>
-    <t>2020-02-05</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2018-01-20</t>
-  </si>
-  <si>
-    <t>2022-07-18</t>
-  </si>
-  <si>
-    <t>2021-04-18</t>
-  </si>
-  <si>
-    <t>2024-07-09</t>
-  </si>
-  <si>
-    <t>2022-04-17</t>
-  </si>
-  <si>
-    <t>2019-02-12</t>
-  </si>
-  <si>
-    <t>2021-06-10</t>
-  </si>
-  <si>
-    <t>2021-05-19</t>
-  </si>
-  <si>
-    <t>2021-07-23</t>
-  </si>
-  <si>
-    <t>2017-05-23</t>
-  </si>
-  <si>
-    <t>2017-10-26</t>
-  </si>
-  <si>
-    <t>2021-08-24</t>
-  </si>
-  <si>
-    <t>2017-02-26</t>
-  </si>
-  <si>
-    <t>2017-12-20</t>
-  </si>
-  <si>
-    <t>2024-05-25</t>
-  </si>
-  <si>
-    <t>2025-03-27</t>
-  </si>
-  <si>
-    <t>2016-07-26</t>
-  </si>
-  <si>
-    <t>2022-04-03</t>
-  </si>
-  <si>
-    <t>2017-06-28</t>
-  </si>
-  <si>
-    <t>2025-06-26</t>
-  </si>
-  <si>
-    <t>2024-04-17</t>
-  </si>
-  <si>
-    <t>2024-09-09</t>
-  </si>
-  <si>
-    <t>2016-06-14</t>
-  </si>
-  <si>
-    <t>2020-11-11</t>
-  </si>
-  <si>
-    <t>2019-05-24</t>
-  </si>
-  <si>
-    <t>2024-01-09</t>
-  </si>
-  <si>
-    <t>2025-08-13</t>
-  </si>
-  <si>
-    <t>2025-04-11</t>
-  </si>
-  <si>
-    <t>2023-07-14</t>
-  </si>
-  <si>
-    <t>2019-09-08</t>
-  </si>
-  <si>
-    <t>2024-12-22</t>
-  </si>
-  <si>
-    <t>2023-06-14</t>
-  </si>
-  <si>
-    <t>2017-07-24</t>
-  </si>
-  <si>
-    <t>2019-12-17</t>
-  </si>
-  <si>
-    <t>2023-09-02</t>
-  </si>
-  <si>
-    <t>2023-05-06</t>
-  </si>
-  <si>
-    <t>2023-07-16</t>
-  </si>
-  <si>
-    <t>2020-03-18</t>
-  </si>
-  <si>
-    <t>2016-05-14</t>
-  </si>
-  <si>
-    <t>2024-04-23</t>
-  </si>
-  <si>
-    <t>2025-08-27</t>
+    <t>2016-05-25</t>
+  </si>
+  <si>
+    <t>2022-10-30</t>
+  </si>
+  <si>
+    <t>2017-04-22</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
+  </si>
+  <si>
+    <t>2023-12-30</t>
+  </si>
+  <si>
+    <t>2023-12-21</t>
+  </si>
+  <si>
+    <t>2024-07-10</t>
+  </si>
+  <si>
+    <t>2020-11-23</t>
+  </si>
+  <si>
+    <t>2025-11-25</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>2017-04-19</t>
+  </si>
+  <si>
+    <t>2022-03-30</t>
+  </si>
+  <si>
+    <t>2024-10-27</t>
+  </si>
+  <si>
+    <t>2017-10-12</t>
   </si>
 </sst>
 </file>
@@ -1689,25 +1692,25 @@
         <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -1722,7 +1725,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -1739,22 +1742,22 @@
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1769,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -1786,22 +1789,22 @@
         <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1816,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
@@ -1830,25 +1833,25 @@
         <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F5" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1863,7 +1866,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -1874,28 +1877,28 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="I6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -1910,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -1921,28 +1924,28 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G7" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="H7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="I7" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1957,7 +1960,7 @@
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -1968,28 +1971,28 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G8" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I8" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -2004,7 +2007,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
@@ -2015,28 +2018,28 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
         <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E9" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -2051,7 +2054,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -2062,28 +2065,28 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G10" t="s">
         <v>215</v>
       </c>
       <c r="H10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="I10" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -2098,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -2109,28 +2112,28 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -2145,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
@@ -2156,28 +2159,28 @@
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E12" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G12" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H12" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="I12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -2192,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
@@ -2203,28 +2206,28 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F13" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G13" t="s">
         <v>214</v>
       </c>
       <c r="H13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I13" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
@@ -2239,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
@@ -2253,25 +2256,25 @@
         <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G14" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="H14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="I14" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -2286,7 +2289,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O14" t="b">
         <v>1</v>
@@ -2297,28 +2300,28 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C15" t="s">
         <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E15" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F15" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G15" t="s">
         <v>215</v>
       </c>
       <c r="H15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I15" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -2333,7 +2336,7 @@
         <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O15" t="b">
         <v>1</v>
@@ -2344,28 +2347,28 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" t="s">
         <v>93</v>
       </c>
-      <c r="C16" t="s">
-        <v>120</v>
-      </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F16" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G16" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H16" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I16" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
@@ -2380,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
@@ -2391,28 +2394,28 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C17" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F17" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G17" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H17" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="I17" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -2427,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="O17" t="b">
         <v>1</v>
@@ -2438,28 +2441,28 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E18" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F18" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G18" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H18" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I18" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
@@ -2474,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O18" t="b">
         <v>1</v>
@@ -2485,28 +2488,28 @@
         <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E19" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F19" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H19" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I19" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2521,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="O19" t="b">
         <v>1</v>
@@ -2532,28 +2535,28 @@
         <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G20" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I20" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -2568,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O20" t="b">
         <v>1</v>
@@ -2579,28 +2582,28 @@
         <v>34</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E21" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F21" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G21" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H21" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I21" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
@@ -2615,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="O21" t="b">
         <v>1</v>
@@ -2626,28 +2629,28 @@
         <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E22" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F22" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G22" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H22" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I22" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
@@ -2662,7 +2665,7 @@
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O22" t="b">
         <v>1</v>
@@ -2673,28 +2676,28 @@
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E23" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F23" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G23" t="s">
         <v>214</v>
       </c>
       <c r="H23" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I23" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
@@ -2709,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="N23" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="O23" t="b">
         <v>1</v>
@@ -2720,28 +2723,28 @@
         <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E24" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F24" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G24" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H24" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I24" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
@@ -2756,7 +2759,7 @@
         <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="O24" t="b">
         <v>1</v>
@@ -2767,28 +2770,28 @@
         <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
         <v>120</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E25" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F25" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G25" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H25" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I25" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
@@ -2803,7 +2806,7 @@
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="O25" t="b">
         <v>1</v>
@@ -2814,28 +2817,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E26" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F26" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G26" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H26" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I26" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
@@ -2850,7 +2853,7 @@
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O26" t="b">
         <v>1</v>
@@ -2861,28 +2864,28 @@
         <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E27" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F27" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G27" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H27" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I27" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
@@ -2897,7 +2900,7 @@
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O27" t="b">
         <v>1</v>
@@ -2908,28 +2911,28 @@
         <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E28" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F28" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G28" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="H28" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I28" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -2944,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O28" t="b">
         <v>1</v>
@@ -2955,28 +2958,28 @@
         <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E29" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F29" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G29" t="s">
         <v>214</v>
       </c>
       <c r="H29" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="I29" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
@@ -2991,7 +2994,7 @@
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
@@ -3002,28 +3005,28 @@
         <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E30" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F30" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G30" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H30" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I30" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3038,7 +3041,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O30" t="b">
         <v>1</v>
@@ -3049,28 +3052,28 @@
         <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E31" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F31" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G31" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H31" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I31" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -3085,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O31" t="b">
         <v>1</v>
@@ -3099,25 +3102,25 @@
         <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E32" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F32" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G32" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H32" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I32" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -3132,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="O32" t="b">
         <v>1</v>
@@ -3143,28 +3146,28 @@
         <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E33" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F33" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G33" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H33" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I33" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -3179,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O33" t="b">
         <v>1</v>
@@ -3190,28 +3193,28 @@
         <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E34" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F34" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G34" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H34" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I34" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
@@ -3226,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O34" t="b">
         <v>1</v>
@@ -3237,28 +3240,28 @@
         <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E35" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F35" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G35" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H35" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I35" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -3273,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O35" t="b">
         <v>1</v>
@@ -3287,25 +3290,25 @@
         <v>105</v>
       </c>
       <c r="C36" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E36" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F36" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G36" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H36" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I36" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -3320,7 +3323,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O36" t="b">
         <v>1</v>
@@ -3331,28 +3334,28 @@
         <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="D37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E37" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F37" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G37" t="s">
         <v>215</v>
       </c>
       <c r="H37" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I37" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -3367,7 +3370,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O37" t="b">
         <v>1</v>
@@ -3378,28 +3381,28 @@
         <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E38" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F38" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G38" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H38" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I38" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -3414,7 +3417,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="O38" t="b">
         <v>1</v>
@@ -3425,28 +3428,28 @@
         <v>52</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E39" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F39" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H39" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I39" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
@@ -3461,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O39" t="b">
         <v>1</v>
@@ -3472,28 +3475,28 @@
         <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E40" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F40" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G40" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H40" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I40" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
@@ -3508,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O40" t="b">
         <v>1</v>
@@ -3519,28 +3522,28 @@
         <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C41" t="s">
-        <v>125</v>
+        <v>93</v>
       </c>
       <c r="D41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E41" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F41" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G41" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H41" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="I41" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
@@ -3555,7 +3558,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O41" t="b">
         <v>1</v>
@@ -3566,28 +3569,28 @@
         <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C42" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="D42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E42" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G42" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H42" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I42" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
@@ -3602,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O42" t="b">
         <v>1</v>
@@ -3613,28 +3616,28 @@
         <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C43" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E43" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F43" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G43" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H43" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="I43" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -3649,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O43" t="b">
         <v>1</v>
@@ -3660,28 +3663,28 @@
         <v>57</v>
       </c>
       <c r="B44" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="D44" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E44" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F44" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G44" t="s">
         <v>214</v>
       </c>
       <c r="H44" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="I44" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
@@ -3696,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O44" t="b">
         <v>1</v>
@@ -3707,28 +3710,28 @@
         <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E45" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F45" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G45" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="H45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="I45" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
@@ -3743,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="O45" t="b">
         <v>1</v>
@@ -3757,25 +3760,25 @@
         <v>91</v>
       </c>
       <c r="C46" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="E46" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F46" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G46" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H46" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I46" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
@@ -3790,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O46" t="b">
         <v>1</v>
@@ -3801,28 +3804,28 @@
         <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D47" t="s">
         <v>175</v>
       </c>
       <c r="E47" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F47" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G47" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H47" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="I47" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
@@ -3837,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O47" t="b">
         <v>1</v>
@@ -3848,28 +3851,28 @@
         <v>61</v>
       </c>
       <c r="B48" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C48" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D48" t="s">
         <v>176</v>
       </c>
       <c r="E48" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F48" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G48" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H48" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I48" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
@@ -3884,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="O48" t="b">
         <v>1</v>
@@ -3895,28 +3898,28 @@
         <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C49" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D49" t="s">
         <v>177</v>
       </c>
       <c r="E49" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F49" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G49" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="H49" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="I49" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
@@ -3931,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O49" t="b">
         <v>1</v>
@@ -3942,28 +3945,28 @@
         <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="C50" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D50" t="s">
         <v>178</v>
       </c>
       <c r="E50" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F50" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G50" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H50" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I50" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
@@ -3978,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O50" t="b">
         <v>1</v>
@@ -3989,28 +3992,28 @@
         <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C51" t="s">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="D51" t="s">
         <v>179</v>
       </c>
       <c r="E51" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F51" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G51" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="H51" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I51" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
@@ -4025,7 +4028,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O51" t="b">
         <v>1</v>
@@ -4036,28 +4039,28 @@
         <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C52" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D52" t="s">
         <v>180</v>
       </c>
       <c r="E52" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F52" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G52" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H52" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I52" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
@@ -4072,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O52" t="b">
         <v>1</v>
@@ -4083,28 +4086,28 @@
         <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C53" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="D53" t="s">
         <v>181</v>
       </c>
       <c r="E53" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F53" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G53" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H53" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I53" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
@@ -4119,7 +4122,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O53" t="b">
         <v>1</v>
@@ -4130,28 +4133,28 @@
         <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C54" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D54" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E54" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F54" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G54" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="H54" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I54" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
@@ -4166,7 +4169,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O54" t="b">
         <v>1</v>
@@ -4177,28 +4180,28 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C55" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D55" t="s">
-        <v>159</v>
+        <v>183</v>
       </c>
       <c r="E55" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F55" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G55" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H55" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="I55" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
@@ -4213,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O55" t="b">
         <v>1</v>
@@ -4224,28 +4227,28 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D56" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="E56" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F56" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G56" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H56" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="I56" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
@@ -4260,7 +4263,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O56" t="b">
         <v>1</v>
@@ -4271,28 +4274,28 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C57" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="D57" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
       <c r="E57" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F57" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G57" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H57" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I57" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -4307,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="N57" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="O57" t="b">
         <v>1</v>
@@ -4318,28 +4321,28 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C58" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D58" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E58" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F58" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G58" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H58" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I58" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -4354,7 +4357,7 @@
         <v>0</v>
       </c>
       <c r="N58" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O58" t="b">
         <v>1</v>
@@ -4365,28 +4368,28 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C59" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D59" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E59" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F59" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G59" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H59" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="I59" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
@@ -4401,7 +4404,7 @@
         <v>0</v>
       </c>
       <c r="N59" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O59" t="b">
         <v>1</v>
@@ -4412,28 +4415,28 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C60" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D60" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E60" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F60" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G60" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H60" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I60" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -4448,7 +4451,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O60" t="b">
         <v>1</v>
@@ -4459,28 +4462,28 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C61" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D61" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="E61" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F61" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G61" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H61" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I61" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -4495,7 +4498,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O61" t="b">
         <v>1</v>
@@ -4506,28 +4509,28 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="D62" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E62" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F62" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G62" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H62" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I62" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -4542,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="N62" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O62" t="b">
         <v>1</v>
@@ -4559,22 +4562,22 @@
         <v>126</v>
       </c>
       <c r="D63" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E63" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F63" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G63" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H63" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I63" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -4589,7 +4592,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="O63" t="b">
         <v>1</v>
@@ -4603,25 +4606,25 @@
         <v>91</v>
       </c>
       <c r="C64" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D64" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H64" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I64" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -4636,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="N64" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O64" t="b">
         <v>1</v>
@@ -4647,28 +4650,28 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C65" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E65" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F65" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G65" t="s">
         <v>213</v>
       </c>
       <c r="H65" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I65" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -4683,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O65" t="b">
         <v>1</v>
@@ -4694,28 +4697,28 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C66" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D66" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="E66" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F66" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G66" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H66" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I66" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -4730,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O66" t="b">
         <v>1</v>
@@ -4741,28 +4744,28 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C67" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D67" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E67" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F67" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G67" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H67" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I67" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -4777,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="N67" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O67" t="b">
         <v>1</v>
@@ -4788,28 +4791,28 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C68" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D68" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E68" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F68" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G68" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H68" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="I68" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -4824,7 +4827,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O68" t="b">
         <v>1</v>
@@ -4835,28 +4838,28 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C69" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D69" t="s">
-        <v>192</v>
+        <v>143</v>
       </c>
       <c r="E69" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F69" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G69" t="s">
         <v>214</v>
       </c>
       <c r="H69" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I69" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
@@ -4871,7 +4874,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O69" t="b">
         <v>1</v>

--- a/datasets/sample_data/staff.xlsx
+++ b/datasets/sample_data/staff.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="427">
   <si>
     <t>Staff_ID</t>
   </si>
@@ -265,340 +265,355 @@
     <t>STF1068</t>
   </si>
   <si>
+    <t>Gwen</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Sarah</t>
+  </si>
+  <si>
+    <t>Geraint</t>
+  </si>
+  <si>
+    <t>Dylan</t>
+  </si>
+  <si>
+    <t>Margaret</t>
+  </si>
+  <si>
+    <t>Angharad</t>
+  </si>
+  <si>
+    <t>Rhian</t>
+  </si>
+  <si>
+    <t>Aled</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Linda</t>
+  </si>
+  <si>
+    <t>Karen</t>
+  </si>
+  <si>
+    <t>Dafydd</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Iwan</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Elizabeth</t>
+  </si>
+  <si>
     <t>Patricia</t>
   </si>
   <si>
+    <t>Susan</t>
+  </si>
+  <si>
+    <t>Robert</t>
+  </si>
+  <si>
+    <t>Bethan</t>
+  </si>
+  <si>
+    <t>Barbara</t>
+  </si>
+  <si>
+    <t>Huw</t>
+  </si>
+  <si>
+    <t>Ffion</t>
+  </si>
+  <si>
+    <t>William</t>
+  </si>
+  <si>
+    <t>Megan</t>
+  </si>
+  <si>
+    <t>Elin</t>
+  </si>
+  <si>
+    <t>Catrin</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
     <t>Jennifer</t>
   </si>
   <si>
-    <t>Mark</t>
-  </si>
-  <si>
-    <t>Megan</t>
-  </si>
-  <si>
-    <t>Susan</t>
-  </si>
-  <si>
-    <t>Emyr</t>
-  </si>
-  <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Linda</t>
-  </si>
-  <si>
-    <t>Aled</t>
-  </si>
-  <si>
-    <t>Dafydd</t>
+    <t>Helen</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Sian</t>
+  </si>
+  <si>
+    <t>Gareth</t>
+  </si>
+  <si>
+    <t>Jenkins</t>
+  </si>
+  <si>
+    <t>Rees</t>
+  </si>
+  <si>
+    <t>Lloyd</t>
+  </si>
+  <si>
+    <t>Edwards</t>
+  </si>
+  <si>
+    <t>Roberts</t>
+  </si>
+  <si>
+    <t>Davies</t>
+  </si>
+  <si>
+    <t>Williams</t>
+  </si>
+  <si>
+    <t>Hughes</t>
+  </si>
+  <si>
+    <t>Jones</t>
+  </si>
+  <si>
+    <t>Griffiths</t>
+  </si>
+  <si>
+    <t>Lewis</t>
+  </si>
+  <si>
+    <t>Price</t>
   </si>
   <si>
     <t>Owen</t>
   </si>
   <si>
-    <t>Iwan</t>
-  </si>
-  <si>
-    <t>Dylan</t>
-  </si>
-  <si>
-    <t>Sarah</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
-    <t>Barbara</t>
-  </si>
-  <si>
-    <t>Angharad</t>
-  </si>
-  <si>
-    <t>Sian</t>
-  </si>
-  <si>
-    <t>Huw</t>
-  </si>
-  <si>
-    <t>Richard</t>
-  </si>
-  <si>
-    <t>Elin</t>
-  </si>
-  <si>
-    <t>William</t>
-  </si>
-  <si>
-    <t>Gareth</t>
-  </si>
-  <si>
-    <t>Elizabeth</t>
-  </si>
-  <si>
-    <t>Rhys</t>
-  </si>
-  <si>
-    <t>Catrin</t>
-  </si>
-  <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Gwen</t>
-  </si>
-  <si>
-    <t>Carys</t>
-  </si>
-  <si>
-    <t>Rees</t>
-  </si>
-  <si>
-    <t>Griffiths</t>
+    <t>Morris</t>
+  </si>
+  <si>
+    <t>Morgan</t>
+  </si>
+  <si>
+    <t>Phillips</t>
   </si>
   <si>
     <t>Powell</t>
   </si>
   <si>
-    <t>Lewis</t>
-  </si>
-  <si>
-    <t>Lloyd</t>
-  </si>
-  <si>
-    <t>Evans</t>
-  </si>
-  <si>
-    <t>Morris</t>
-  </si>
-  <si>
-    <t>Phillips</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>Jones</t>
-  </si>
-  <si>
-    <t>Morgan</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Roberts</t>
-  </si>
-  <si>
-    <t>Jenkins</t>
-  </si>
-  <si>
-    <t>Hughes</t>
-  </si>
-  <si>
-    <t>Davies</t>
-  </si>
-  <si>
-    <t>Edwards</t>
-  </si>
-  <si>
-    <t>Patricia Rees</t>
-  </si>
-  <si>
-    <t>Jennifer Griffiths</t>
-  </si>
-  <si>
-    <t>Mark Powell</t>
-  </si>
-  <si>
-    <t>Megan Owen</t>
-  </si>
-  <si>
-    <t>Jennifer Lewis</t>
-  </si>
-  <si>
-    <t>Jennifer Lloyd</t>
-  </si>
-  <si>
-    <t>Susan Powell</t>
-  </si>
-  <si>
-    <t>Emyr Evans</t>
-  </si>
-  <si>
-    <t>David Morris</t>
-  </si>
-  <si>
-    <t>Linda Phillips</t>
-  </si>
-  <si>
-    <t>Jennifer Evans</t>
-  </si>
-  <si>
-    <t>Aled Powell</t>
-  </si>
-  <si>
-    <t>Dafydd Owen</t>
-  </si>
-  <si>
-    <t>Owen James</t>
-  </si>
-  <si>
-    <t>Jennifer Owen</t>
-  </si>
-  <si>
-    <t>Iwan Jones</t>
-  </si>
-  <si>
-    <t>Dylan Lloyd</t>
-  </si>
-  <si>
-    <t>Sarah Morgan</t>
-  </si>
-  <si>
-    <t>Paul Evans</t>
-  </si>
-  <si>
-    <t>Barbara Price</t>
-  </si>
-  <si>
-    <t>Angharad Morgan</t>
-  </si>
-  <si>
-    <t>Megan Roberts</t>
-  </si>
-  <si>
-    <t>Owen Owen</t>
-  </si>
-  <si>
-    <t>Sian Phillips</t>
-  </si>
-  <si>
-    <t>Huw Evans</t>
-  </si>
-  <si>
-    <t>Richard Price</t>
-  </si>
-  <si>
-    <t>Dylan Jenkins</t>
-  </si>
-  <si>
-    <t>Elin Morgan</t>
+    <t>Gwen Jenkins</t>
+  </si>
+  <si>
+    <t>John James</t>
+  </si>
+  <si>
+    <t>Paul Jenkins</t>
+  </si>
+  <si>
+    <t>Sarah Rees</t>
+  </si>
+  <si>
+    <t>Geraint Lloyd</t>
+  </si>
+  <si>
+    <t>Dylan Edwards</t>
+  </si>
+  <si>
+    <t>Geraint James</t>
+  </si>
+  <si>
+    <t>Margaret Jenkins</t>
+  </si>
+  <si>
+    <t>Angharad Roberts</t>
+  </si>
+  <si>
+    <t>Rhian Edwards</t>
+  </si>
+  <si>
+    <t>Aled Davies</t>
+  </si>
+  <si>
+    <t>Angharad Williams</t>
+  </si>
+  <si>
+    <t>David James</t>
+  </si>
+  <si>
+    <t>Linda Hughes</t>
+  </si>
+  <si>
+    <t>Karen Jones</t>
+  </si>
+  <si>
+    <t>Gwen Davies</t>
+  </si>
+  <si>
+    <t>Angharad Rees</t>
+  </si>
+  <si>
+    <t>Dafydd Rees</t>
+  </si>
+  <si>
+    <t>James Jenkins</t>
+  </si>
+  <si>
+    <t>Iwan Lloyd</t>
+  </si>
+  <si>
+    <t>Thomas Griffiths</t>
+  </si>
+  <si>
+    <t>Elizabeth Lewis</t>
+  </si>
+  <si>
+    <t>Patricia Lloyd</t>
+  </si>
+  <si>
+    <t>Susan Price</t>
+  </si>
+  <si>
+    <t>Paul Owen</t>
+  </si>
+  <si>
+    <t>Dylan Hughes</t>
+  </si>
+  <si>
+    <t>Robert Hughes</t>
+  </si>
+  <si>
+    <t>Bethan James</t>
+  </si>
+  <si>
+    <t>Barbara Rees</t>
+  </si>
+  <si>
+    <t>Dafydd Hughes</t>
+  </si>
+  <si>
+    <t>Huw Hughes</t>
+  </si>
+  <si>
+    <t>Gwen Rees</t>
+  </si>
+  <si>
+    <t>Aled Morris</t>
+  </si>
+  <si>
+    <t>Dylan Morgan</t>
+  </si>
+  <si>
+    <t>Bethan Davies</t>
+  </si>
+  <si>
+    <t>Angharad Jenkins</t>
+  </si>
+  <si>
+    <t>Ffion Davies</t>
+  </si>
+  <si>
+    <t>Elizabeth Lloyd</t>
+  </si>
+  <si>
+    <t>William Davies</t>
+  </si>
+  <si>
+    <t>Sarah Phillips</t>
+  </si>
+  <si>
+    <t>Thomas Williams</t>
+  </si>
+  <si>
+    <t>Paul Griffiths</t>
+  </si>
+  <si>
+    <t>Megan Powell</t>
+  </si>
+  <si>
+    <t>Elin Roberts</t>
+  </si>
+  <si>
+    <t>Catrin Thomas</t>
+  </si>
+  <si>
+    <t>Elizabeth Davies</t>
+  </si>
+  <si>
+    <t>Mark Lloyd</t>
   </si>
   <si>
     <t>William Morgan</t>
   </si>
   <si>
-    <t>Paul Price</t>
-  </si>
-  <si>
-    <t>Owen Price</t>
-  </si>
-  <si>
-    <t>Paul Morris</t>
-  </si>
-  <si>
-    <t>Gareth Hughes</t>
-  </si>
-  <si>
-    <t>Sarah Powell</t>
-  </si>
-  <si>
-    <t>Gareth Morris</t>
-  </si>
-  <si>
-    <t>Huw Morris</t>
-  </si>
-  <si>
-    <t>Barbara Griffiths</t>
-  </si>
-  <si>
-    <t>Elizabeth Evans</t>
-  </si>
-  <si>
-    <t>Susan Jenkins</t>
+    <t>Jennifer Jenkins</t>
+  </si>
+  <si>
+    <t>Patricia Thomas</t>
+  </si>
+  <si>
+    <t>Sarah Jones</t>
+  </si>
+  <si>
+    <t>Mark Morgan</t>
+  </si>
+  <si>
+    <t>Rhian Powell</t>
+  </si>
+  <si>
+    <t>Helen Morgan</t>
+  </si>
+  <si>
+    <t>Huw Lloyd</t>
+  </si>
+  <si>
+    <t>Gwen Lewis</t>
+  </si>
+  <si>
+    <t>Mark Rees</t>
+  </si>
+  <si>
+    <t>Ffion Griffiths</t>
+  </si>
+  <si>
+    <t>Susan Lewis</t>
   </si>
   <si>
     <t>Richard Owen</t>
   </si>
   <si>
-    <t>Iwan Davies</t>
-  </si>
-  <si>
-    <t>Rhys Griffiths</t>
-  </si>
-  <si>
-    <t>David Jenkins</t>
-  </si>
-  <si>
-    <t>Elin Davies</t>
-  </si>
-  <si>
-    <t>Aled Rees</t>
-  </si>
-  <si>
-    <t>Sarah Price</t>
-  </si>
-  <si>
-    <t>Catrin Jones</t>
-  </si>
-  <si>
-    <t>David Jones</t>
-  </si>
-  <si>
-    <t>Megan Jones</t>
-  </si>
-  <si>
-    <t>Elizabeth James</t>
-  </si>
-  <si>
-    <t>Thomas Powell</t>
-  </si>
-  <si>
-    <t>John Rees</t>
-  </si>
-  <si>
-    <t>Gareth Edwards</t>
-  </si>
-  <si>
-    <t>Angharad Price</t>
-  </si>
-  <si>
-    <t>Iwan Lewis</t>
-  </si>
-  <si>
-    <t>Gwen Rees</t>
-  </si>
-  <si>
-    <t>Mark Griffiths</t>
-  </si>
-  <si>
-    <t>Carys Edwards</t>
-  </si>
-  <si>
-    <t>Iwan Morgan</t>
-  </si>
-  <si>
-    <t>Jennifer Davies</t>
-  </si>
-  <si>
-    <t>Huw Jenkins</t>
-  </si>
-  <si>
-    <t>Aled Price</t>
-  </si>
-  <si>
-    <t>Gwen Jones</t>
-  </si>
-  <si>
-    <t>Paul Roberts</t>
-  </si>
-  <si>
-    <t>Carys Morgan</t>
+    <t>Susan Morgan</t>
+  </si>
+  <si>
+    <t>Sian James</t>
+  </si>
+  <si>
+    <t>Elizabeth Williams</t>
+  </si>
+  <si>
+    <t>Gareth James</t>
+  </si>
+  <si>
+    <t>Patricia Roberts</t>
   </si>
   <si>
     <t>SACT Nurse</t>
@@ -655,21 +670,21 @@
     <t>Band 4</t>
   </si>
   <si>
+    <t>RGH</t>
+  </si>
+  <si>
     <t>POW</t>
   </si>
   <si>
+    <t>CWM</t>
+  </si>
+  <si>
+    <t>PCH</t>
+  </si>
+  <si>
     <t>WC</t>
   </si>
   <si>
-    <t>RGH</t>
-  </si>
-  <si>
-    <t>CWM</t>
-  </si>
-  <si>
-    <t>PCH</t>
-  </si>
-  <si>
     <t>staff1001@velindre.nhs.wales</t>
   </si>
   <si>
@@ -874,409 +889,412 @@
     <t>staff1068@velindre.nhs.wales</t>
   </si>
   <si>
-    <t>4914</t>
-  </si>
-  <si>
-    <t>3258</t>
-  </si>
-  <si>
-    <t>6145</t>
-  </si>
-  <si>
-    <t>7882</t>
-  </si>
-  <si>
-    <t>1586</t>
-  </si>
-  <si>
-    <t>5277</t>
-  </si>
-  <si>
-    <t>7134</t>
-  </si>
-  <si>
-    <t>3035</t>
-  </si>
-  <si>
-    <t>6668</t>
-  </si>
-  <si>
-    <t>9365</t>
-  </si>
-  <si>
-    <t>9233</t>
-  </si>
-  <si>
-    <t>1640</t>
-  </si>
-  <si>
-    <t>2376</t>
-  </si>
-  <si>
-    <t>3232</t>
-  </si>
-  <si>
-    <t>4359</t>
-  </si>
-  <si>
-    <t>1589</t>
-  </si>
-  <si>
-    <t>9017</t>
-  </si>
-  <si>
-    <t>4298</t>
-  </si>
-  <si>
-    <t>5584</t>
-  </si>
-  <si>
-    <t>2179</t>
-  </si>
-  <si>
-    <t>3946</t>
-  </si>
-  <si>
-    <t>6974</t>
-  </si>
-  <si>
-    <t>2982</t>
-  </si>
-  <si>
-    <t>8735</t>
-  </si>
-  <si>
-    <t>6189</t>
-  </si>
-  <si>
-    <t>6975</t>
-  </si>
-  <si>
-    <t>8746</t>
-  </si>
-  <si>
-    <t>5211</t>
-  </si>
-  <si>
-    <t>2160</t>
-  </si>
-  <si>
-    <t>2813</t>
-  </si>
-  <si>
-    <t>3404</t>
-  </si>
-  <si>
-    <t>6394</t>
-  </si>
-  <si>
-    <t>8960</t>
-  </si>
-  <si>
-    <t>5063</t>
-  </si>
-  <si>
-    <t>3160</t>
-  </si>
-  <si>
-    <t>5542</t>
-  </si>
-  <si>
-    <t>9967</t>
-  </si>
-  <si>
-    <t>4362</t>
-  </si>
-  <si>
-    <t>5217</t>
-  </si>
-  <si>
-    <t>2864</t>
-  </si>
-  <si>
-    <t>8916</t>
-  </si>
-  <si>
-    <t>3687</t>
-  </si>
-  <si>
-    <t>3990</t>
-  </si>
-  <si>
-    <t>3057</t>
-  </si>
-  <si>
-    <t>3700</t>
-  </si>
-  <si>
-    <t>7789</t>
-  </si>
-  <si>
-    <t>2057</t>
-  </si>
-  <si>
-    <t>8380</t>
-  </si>
-  <si>
-    <t>7115</t>
-  </si>
-  <si>
-    <t>2877</t>
-  </si>
-  <si>
-    <t>2569</t>
-  </si>
-  <si>
-    <t>2402</t>
-  </si>
-  <si>
-    <t>7209</t>
-  </si>
-  <si>
-    <t>3111</t>
-  </si>
-  <si>
-    <t>8956</t>
-  </si>
-  <si>
-    <t>4779</t>
-  </si>
-  <si>
-    <t>1963</t>
-  </si>
-  <si>
-    <t>3668</t>
-  </si>
-  <si>
-    <t>7807</t>
-  </si>
-  <si>
-    <t>5479</t>
-  </si>
-  <si>
-    <t>4090</t>
-  </si>
-  <si>
-    <t>1372</t>
-  </si>
-  <si>
-    <t>6561</t>
-  </si>
-  <si>
-    <t>4514</t>
-  </si>
-  <si>
-    <t>7631</t>
-  </si>
-  <si>
-    <t>3581</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>4010</t>
-  </si>
-  <si>
-    <t>2019-05-07</t>
-  </si>
-  <si>
-    <t>2024-12-17</t>
-  </si>
-  <si>
-    <t>2019-06-08</t>
-  </si>
-  <si>
-    <t>2019-08-21</t>
-  </si>
-  <si>
-    <t>2017-08-04</t>
-  </si>
-  <si>
-    <t>2021-02-19</t>
-  </si>
-  <si>
-    <t>2019-05-05</t>
-  </si>
-  <si>
-    <t>2017-03-10</t>
-  </si>
-  <si>
-    <t>2022-01-01</t>
-  </si>
-  <si>
-    <t>2025-12-09</t>
-  </si>
-  <si>
-    <t>2019-08-18</t>
-  </si>
-  <si>
-    <t>2025-02-24</t>
-  </si>
-  <si>
-    <t>2016-08-28</t>
-  </si>
-  <si>
-    <t>2019-11-14</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>2016-09-29</t>
-  </si>
-  <si>
-    <t>2023-06-17</t>
-  </si>
-  <si>
-    <t>2019-10-26</t>
-  </si>
-  <si>
-    <t>2016-07-09</t>
-  </si>
-  <si>
-    <t>2019-08-16</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>2022-11-27</t>
-  </si>
-  <si>
-    <t>2023-06-08</t>
-  </si>
-  <si>
-    <t>2021-05-02</t>
-  </si>
-  <si>
-    <t>2025-07-14</t>
-  </si>
-  <si>
-    <t>2025-01-25</t>
-  </si>
-  <si>
-    <t>2019-07-10</t>
-  </si>
-  <si>
-    <t>2023-09-07</t>
-  </si>
-  <si>
-    <t>2020-05-20</t>
-  </si>
-  <si>
-    <t>2024-05-19</t>
-  </si>
-  <si>
-    <t>2018-07-19</t>
-  </si>
-  <si>
-    <t>2018-11-08</t>
-  </si>
-  <si>
-    <t>2016-04-30</t>
-  </si>
-  <si>
-    <t>2020-02-23</t>
-  </si>
-  <si>
-    <t>2016-05-22</t>
-  </si>
-  <si>
-    <t>2018-10-08</t>
-  </si>
-  <si>
-    <t>2017-04-06</t>
-  </si>
-  <si>
-    <t>2017-02-07</t>
-  </si>
-  <si>
-    <t>2024-08-01</t>
-  </si>
-  <si>
-    <t>2023-10-20</t>
-  </si>
-  <si>
-    <t>2018-08-05</t>
-  </si>
-  <si>
-    <t>2020-08-25</t>
-  </si>
-  <si>
-    <t>2023-09-10</t>
-  </si>
-  <si>
-    <t>2021-12-06</t>
-  </si>
-  <si>
-    <t>2022-08-23</t>
-  </si>
-  <si>
-    <t>2017-04-23</t>
-  </si>
-  <si>
-    <t>2019-02-02</t>
-  </si>
-  <si>
-    <t>2022-05-31</t>
-  </si>
-  <si>
-    <t>2023-04-09</t>
-  </si>
-  <si>
-    <t>2021-04-01</t>
-  </si>
-  <si>
-    <t>2017-04-16</t>
-  </si>
-  <si>
-    <t>2022-10-19</t>
-  </si>
-  <si>
-    <t>2020-12-19</t>
-  </si>
-  <si>
-    <t>2016-05-25</t>
-  </si>
-  <si>
-    <t>2022-10-30</t>
-  </si>
-  <si>
-    <t>2017-04-22</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
-  </si>
-  <si>
-    <t>2023-12-30</t>
-  </si>
-  <si>
-    <t>2023-12-21</t>
-  </si>
-  <si>
-    <t>2024-07-10</t>
-  </si>
-  <si>
-    <t>2020-11-23</t>
-  </si>
-  <si>
-    <t>2025-11-25</t>
-  </si>
-  <si>
-    <t>2021-09-03</t>
-  </si>
-  <si>
-    <t>2017-04-19</t>
-  </si>
-  <si>
-    <t>2022-03-30</t>
-  </si>
-  <si>
-    <t>2024-10-27</t>
-  </si>
-  <si>
-    <t>2017-10-12</t>
+    <t>9678</t>
+  </si>
+  <si>
+    <t>3836</t>
+  </si>
+  <si>
+    <t>1364</t>
+  </si>
+  <si>
+    <t>3559</t>
+  </si>
+  <si>
+    <t>2950</t>
+  </si>
+  <si>
+    <t>7382</t>
+  </si>
+  <si>
+    <t>5388</t>
+  </si>
+  <si>
+    <t>8287</t>
+  </si>
+  <si>
+    <t>2522</t>
+  </si>
+  <si>
+    <t>9649</t>
+  </si>
+  <si>
+    <t>9692</t>
+  </si>
+  <si>
+    <t>1883</t>
+  </si>
+  <si>
+    <t>2566</t>
+  </si>
+  <si>
+    <t>4588</t>
+  </si>
+  <si>
+    <t>3278</t>
+  </si>
+  <si>
+    <t>1746</t>
+  </si>
+  <si>
+    <t>1605</t>
+  </si>
+  <si>
+    <t>9603</t>
+  </si>
+  <si>
+    <t>2644</t>
+  </si>
+  <si>
+    <t>5067</t>
+  </si>
+  <si>
+    <t>5106</t>
+  </si>
+  <si>
+    <t>7773</t>
+  </si>
+  <si>
+    <t>7256</t>
+  </si>
+  <si>
+    <t>4860</t>
+  </si>
+  <si>
+    <t>5755</t>
+  </si>
+  <si>
+    <t>8745</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>9681</t>
+  </si>
+  <si>
+    <t>8994</t>
+  </si>
+  <si>
+    <t>3742</t>
+  </si>
+  <si>
+    <t>9096</t>
+  </si>
+  <si>
+    <t>1494</t>
+  </si>
+  <si>
+    <t>8662</t>
+  </si>
+  <si>
+    <t>8719</t>
+  </si>
+  <si>
+    <t>3354</t>
+  </si>
+  <si>
+    <t>7708</t>
+  </si>
+  <si>
+    <t>8090</t>
+  </si>
+  <si>
+    <t>1817</t>
+  </si>
+  <si>
+    <t>9864</t>
+  </si>
+  <si>
+    <t>1768</t>
+  </si>
+  <si>
+    <t>3505</t>
+  </si>
+  <si>
+    <t>3807</t>
+  </si>
+  <si>
+    <t>2803</t>
+  </si>
+  <si>
+    <t>1913</t>
+  </si>
+  <si>
+    <t>2542</t>
+  </si>
+  <si>
+    <t>3810</t>
+  </si>
+  <si>
+    <t>2471</t>
+  </si>
+  <si>
+    <t>9067</t>
+  </si>
+  <si>
+    <t>3555</t>
+  </si>
+  <si>
+    <t>7780</t>
+  </si>
+  <si>
+    <t>1022</t>
+  </si>
+  <si>
+    <t>6590</t>
+  </si>
+  <si>
+    <t>8785</t>
+  </si>
+  <si>
+    <t>6600</t>
+  </si>
+  <si>
+    <t>5244</t>
+  </si>
+  <si>
+    <t>1868</t>
+  </si>
+  <si>
+    <t>2625</t>
+  </si>
+  <si>
+    <t>6070</t>
+  </si>
+  <si>
+    <t>1956</t>
+  </si>
+  <si>
+    <t>9101</t>
+  </si>
+  <si>
+    <t>3238</t>
+  </si>
+  <si>
+    <t>5661</t>
+  </si>
+  <si>
+    <t>3859</t>
+  </si>
+  <si>
+    <t>3666</t>
+  </si>
+  <si>
+    <t>1927</t>
+  </si>
+  <si>
+    <t>4912</t>
+  </si>
+  <si>
+    <t>5187</t>
+  </si>
+  <si>
+    <t>5911</t>
+  </si>
+  <si>
+    <t>2024-02-16</t>
+  </si>
+  <si>
+    <t>2020-03-22</t>
+  </si>
+  <si>
+    <t>2016-10-11</t>
+  </si>
+  <si>
+    <t>2022-03-14</t>
+  </si>
+  <si>
+    <t>2026-03-26</t>
+  </si>
+  <si>
+    <t>2020-04-03</t>
+  </si>
+  <si>
+    <t>2022-01-30</t>
+  </si>
+  <si>
+    <t>2019-03-11</t>
+  </si>
+  <si>
+    <t>2026-01-26</t>
+  </si>
+  <si>
+    <t>2024-09-26</t>
+  </si>
+  <si>
+    <t>2021-01-09</t>
+  </si>
+  <si>
+    <t>2024-01-13</t>
+  </si>
+  <si>
+    <t>2019-03-04</t>
+  </si>
+  <si>
+    <t>2018-02-25</t>
+  </si>
+  <si>
+    <t>2023-09-14</t>
+  </si>
+  <si>
+    <t>2019-02-09</t>
+  </si>
+  <si>
+    <t>2018-08-17</t>
+  </si>
+  <si>
+    <t>2019-08-13</t>
+  </si>
+  <si>
+    <t>2017-01-29</t>
+  </si>
+  <si>
+    <t>2018-01-15</t>
+  </si>
+  <si>
+    <t>2017-01-20</t>
+  </si>
+  <si>
+    <t>2021-09-13</t>
+  </si>
+  <si>
+    <t>2023-08-04</t>
+  </si>
+  <si>
+    <t>2020-02-14</t>
+  </si>
+  <si>
+    <t>2024-02-05</t>
+  </si>
+  <si>
+    <t>2021-02-02</t>
+  </si>
+  <si>
+    <t>2019-09-14</t>
+  </si>
+  <si>
+    <t>2022-11-03</t>
+  </si>
+  <si>
+    <t>2021-05-06</t>
+  </si>
+  <si>
+    <t>2021-10-04</t>
+  </si>
+  <si>
+    <t>2021-08-20</t>
+  </si>
+  <si>
+    <t>2018-04-14</t>
+  </si>
+  <si>
+    <t>2018-08-14</t>
+  </si>
+  <si>
+    <t>2017-04-29</t>
+  </si>
+  <si>
+    <t>2023-12-14</t>
+  </si>
+  <si>
+    <t>2018-01-25</t>
+  </si>
+  <si>
+    <t>2016-11-07</t>
+  </si>
+  <si>
+    <t>2021-04-04</t>
+  </si>
+  <si>
+    <t>2023-08-21</t>
+  </si>
+  <si>
+    <t>2019-09-15</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2025-05-05</t>
+  </si>
+  <si>
+    <t>2020-03-29</t>
+  </si>
+  <si>
+    <t>2017-08-03</t>
+  </si>
+  <si>
+    <t>2020-11-22</t>
+  </si>
+  <si>
+    <t>2023-04-28</t>
+  </si>
+  <si>
+    <t>2020-12-18</t>
+  </si>
+  <si>
+    <t>2025-06-22</t>
+  </si>
+  <si>
+    <t>2017-05-25</t>
+  </si>
+  <si>
+    <t>2026-03-24</t>
+  </si>
+  <si>
+    <t>2021-09-19</t>
+  </si>
+  <si>
+    <t>2022-11-29</t>
+  </si>
+  <si>
+    <t>2025-10-28</t>
+  </si>
+  <si>
+    <t>2020-11-29</t>
+  </si>
+  <si>
+    <t>2022-07-04</t>
+  </si>
+  <si>
+    <t>2025-09-14</t>
+  </si>
+  <si>
+    <t>2020-09-10</t>
+  </si>
+  <si>
+    <t>2018-03-17</t>
+  </si>
+  <si>
+    <t>2024-01-02</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2023-03-19</t>
+  </si>
+  <si>
+    <t>2017-03-14</t>
+  </si>
+  <si>
+    <t>2019-09-12</t>
+  </si>
+  <si>
+    <t>2017-01-15</t>
+  </si>
+  <si>
+    <t>2017-01-17</t>
+  </si>
+  <si>
+    <t>2024-08-03</t>
+  </si>
+  <si>
+    <t>2022-12-04</t>
   </si>
 </sst>
 </file>
@@ -1692,25 +1710,25 @@
         <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="I2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -1725,7 +1743,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -1739,25 +1757,25 @@
         <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F3" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I3" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -1772,7 +1790,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -1786,25 +1804,25 @@
         <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="I4" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -1819,7 +1837,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
@@ -1833,25 +1851,25 @@
         <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F5" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H5" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="I5" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -1866,7 +1884,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -1877,28 +1895,28 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H6" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="I6" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -1913,7 +1931,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -1924,28 +1942,28 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F7" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G7" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="H7" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I7" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -1960,7 +1978,7 @@
         <v>1</v>
       </c>
       <c r="N7" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -1974,25 +1992,25 @@
         <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F8" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H8" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="I8" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -2007,7 +2025,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
@@ -2018,28 +2036,28 @@
         <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
         <v>118</v>
       </c>
       <c r="D9" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E9" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F9" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G9" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H9" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I9" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
@@ -2054,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -2065,28 +2083,28 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F10" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G10" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H10" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="I10" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
@@ -2101,7 +2119,7 @@
         <v>1</v>
       </c>
       <c r="N10" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -2112,28 +2130,28 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F11" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G11" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H11" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I11" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
@@ -2148,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
@@ -2159,28 +2177,28 @@
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E12" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F12" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G12" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H12" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="I12" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
@@ -2195,7 +2213,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
@@ -2206,28 +2224,28 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F13" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G13" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H13" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="I13" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
@@ -2242,7 +2260,7 @@
         <v>1</v>
       </c>
       <c r="N13" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="O13" t="b">
         <v>1</v>
@@ -2253,28 +2271,28 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="E14" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F14" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G14" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="I14" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
@@ -2289,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O14" t="b">
         <v>1</v>
@@ -2300,28 +2318,28 @@
         <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F15" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G15" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H15" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I15" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
@@ -2336,7 +2354,7 @@
         <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="O15" t="b">
         <v>1</v>
@@ -2347,28 +2365,28 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="D16" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E16" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F16" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G16" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H16" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="I16" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
@@ -2383,7 +2401,7 @@
         <v>1</v>
       </c>
       <c r="N16" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="O16" t="b">
         <v>1</v>
@@ -2394,28 +2412,28 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E17" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F17" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G17" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H17" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I17" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
@@ -2430,7 +2448,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="O17" t="b">
         <v>1</v>
@@ -2441,28 +2459,28 @@
         <v>31</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E18" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F18" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G18" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H18" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="I18" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
@@ -2477,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="N18" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="O18" t="b">
         <v>1</v>
@@ -2491,25 +2509,25 @@
         <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E19" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F19" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G19" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="H19" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="I19" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
@@ -2524,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="N19" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="O19" t="b">
         <v>1</v>
@@ -2541,22 +2559,22 @@
         <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E20" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F20" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G20" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H20" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I20" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
@@ -2571,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="N20" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="O20" t="b">
         <v>1</v>
@@ -2585,25 +2603,25 @@
         <v>98</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F21" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="G21" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="H21" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="I21" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
@@ -2618,7 +2636,7 @@
         <v>1</v>
       </c>
       <c r="N21" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="O21" t="b">
         <v>1</v>
@@ -2632,25 +2650,25 @@
         <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E22" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F22" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G22" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H22" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="I22" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
@@ -2665,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="O22" t="b">
         <v>1</v>
@@ -2676,28 +2694,28 @@
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D23" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F23" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G23" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H23" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="I23" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
@@ -2712,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="N23" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="O23" t="b">
         <v>1</v>
@@ -2723,28 +2741,28 @@
         <v>37</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="E24" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F24" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G24" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H24" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="I24" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
@@ -2759,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="N24" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="O24" t="b">
         <v>1</v>
@@ -2770,28 +2788,28 @@
         <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E25" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F25" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G25" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H25" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="I25" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
@@ -2806,7 +2824,7 @@
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="O25" t="b">
         <v>1</v>
@@ -2817,28 +2835,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G26" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H26" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="I26" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
@@ -2853,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="N26" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="O26" t="b">
         <v>1</v>
@@ -2864,28 +2882,28 @@
         <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D27" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E27" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F27" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G27" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H27" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="I27" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
@@ -2900,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="N27" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="O27" t="b">
         <v>1</v>
@@ -2911,28 +2929,28 @@
         <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="E28" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F28" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G28" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H28" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I28" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -2947,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="O28" t="b">
         <v>1</v>
@@ -2958,28 +2976,28 @@
         <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E29" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F29" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G29" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="H29" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I29" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
@@ -2994,7 +3012,7 @@
         <v>1</v>
       </c>
       <c r="N29" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="O29" t="b">
         <v>1</v>
@@ -3005,28 +3023,28 @@
         <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E30" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F30" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G30" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H30" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="I30" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -3041,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="O30" t="b">
         <v>1</v>
@@ -3052,28 +3070,28 @@
         <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E31" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F31" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G31" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H31" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="I31" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J31" t="b">
         <v>0</v>
@@ -3088,7 +3106,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="O31" t="b">
         <v>1</v>
@@ -3099,28 +3117,28 @@
         <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E32" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F32" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G32" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H32" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I32" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="J32" t="b">
         <v>0</v>
@@ -3135,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="O32" t="b">
         <v>1</v>
@@ -3146,28 +3164,28 @@
         <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C33" t="s">
         <v>119</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E33" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F33" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G33" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H33" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I33" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="J33" t="b">
         <v>0</v>
@@ -3182,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="N33" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="O33" t="b">
         <v>1</v>
@@ -3193,28 +3211,28 @@
         <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="E34" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F34" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G34" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H34" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="I34" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="J34" t="b">
         <v>0</v>
@@ -3229,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="O34" t="b">
         <v>1</v>
@@ -3240,28 +3258,28 @@
         <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E35" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F35" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G35" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="H35" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="I35" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
@@ -3276,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="O35" t="b">
         <v>1</v>
@@ -3287,28 +3305,28 @@
         <v>49</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D36" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E36" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F36" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G36" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H36" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="I36" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="J36" t="b">
         <v>0</v>
@@ -3323,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="O36" t="b">
         <v>1</v>
@@ -3334,28 +3352,28 @@
         <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E37" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F37" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G37" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H37" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="I37" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="J37" t="b">
         <v>0</v>
@@ -3370,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="N37" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="O37" t="b">
         <v>1</v>
@@ -3381,28 +3399,28 @@
         <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D38" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="E38" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F38" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G38" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H38" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="I38" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J38" t="b">
         <v>0</v>
@@ -3417,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="O38" t="b">
         <v>1</v>
@@ -3428,28 +3446,28 @@
         <v>52</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D39" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="E39" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F39" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G39" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H39" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="I39" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="J39" t="b">
         <v>0</v>
@@ -3464,7 +3482,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="O39" t="b">
         <v>1</v>
@@ -3475,28 +3493,28 @@
         <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C40" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D40" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E40" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F40" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G40" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H40" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="I40" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="J40" t="b">
         <v>0</v>
@@ -3511,7 +3529,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="O40" t="b">
         <v>1</v>
@@ -3522,28 +3540,28 @@
         <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="D41" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E41" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F41" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G41" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H41" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="I41" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J41" t="b">
         <v>0</v>
@@ -3558,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="O41" t="b">
         <v>1</v>
@@ -3569,28 +3587,28 @@
         <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="D42" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E42" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F42" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G42" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H42" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="I42" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="J42" t="b">
         <v>0</v>
@@ -3605,7 +3623,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="O42" t="b">
         <v>1</v>
@@ -3616,28 +3634,28 @@
         <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D43" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="E43" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G43" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H43" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="I43" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="J43" t="b">
         <v>0</v>
@@ -3652,7 +3670,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="O43" t="b">
         <v>1</v>
@@ -3663,28 +3681,28 @@
         <v>57</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E44" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F44" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G44" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H44" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="I44" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="J44" t="b">
         <v>0</v>
@@ -3699,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="O44" t="b">
         <v>1</v>
@@ -3710,28 +3728,28 @@
         <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C45" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="D45" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E45" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F45" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G45" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H45" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="I45" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="J45" t="b">
         <v>0</v>
@@ -3746,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="O45" t="b">
         <v>1</v>
@@ -3757,28 +3775,28 @@
         <v>59</v>
       </c>
       <c r="B46" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C46" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="D46" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="E46" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F46" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G46" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="H46" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="I46" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="J46" t="b">
         <v>0</v>
@@ -3793,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="O46" t="b">
         <v>1</v>
@@ -3804,28 +3822,28 @@
         <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D47" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E47" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F47" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G47" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H47" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="I47" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J47" t="b">
         <v>0</v>
@@ -3840,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="O47" t="b">
         <v>1</v>
@@ -3851,28 +3869,28 @@
         <v>61</v>
       </c>
       <c r="B48" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D48" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="E48" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F48" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G48" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="H48" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="I48" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J48" t="b">
         <v>0</v>
@@ -3887,7 +3905,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="O48" t="b">
         <v>1</v>
@@ -3898,28 +3916,28 @@
         <v>62</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D49" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E49" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F49" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G49" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H49" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="I49" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J49" t="b">
         <v>0</v>
@@ -3934,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="O49" t="b">
         <v>1</v>
@@ -3945,28 +3963,28 @@
         <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D50" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E50" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F50" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G50" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H50" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="I50" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J50" t="b">
         <v>0</v>
@@ -3981,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="O50" t="b">
         <v>1</v>
@@ -3992,28 +4010,28 @@
         <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D51" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="E51" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F51" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G51" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H51" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I51" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J51" t="b">
         <v>0</v>
@@ -4028,7 +4046,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="O51" t="b">
         <v>1</v>
@@ -4039,28 +4057,28 @@
         <v>65</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="C52" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D52" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="E52" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F52" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G52" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H52" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="I52" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J52" t="b">
         <v>0</v>
@@ -4075,7 +4093,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="O52" t="b">
         <v>1</v>
@@ -4086,28 +4104,28 @@
         <v>66</v>
       </c>
       <c r="B53" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="D53" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E53" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F53" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G53" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H53" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I53" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J53" t="b">
         <v>0</v>
@@ -4122,7 +4140,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="O53" t="b">
         <v>1</v>
@@ -4133,28 +4151,28 @@
         <v>67</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D54" t="s">
-        <v>182</v>
+        <v>146</v>
       </c>
       <c r="E54" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F54" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G54" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="H54" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="I54" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J54" t="b">
         <v>0</v>
@@ -4169,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="O54" t="b">
         <v>1</v>
@@ -4180,28 +4198,28 @@
         <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C55" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D55" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E55" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F55" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G55" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H55" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="I55" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J55" t="b">
         <v>0</v>
@@ -4216,7 +4234,7 @@
         <v>0</v>
       </c>
       <c r="N55" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="O55" t="b">
         <v>1</v>
@@ -4227,28 +4245,28 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="D56" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E56" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F56" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G56" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="H56" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="I56" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J56" t="b">
         <v>0</v>
@@ -4263,7 +4281,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="O56" t="b">
         <v>1</v>
@@ -4274,28 +4292,28 @@
         <v>70</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="C57" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D57" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="E57" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F57" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G57" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="H57" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="I57" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
@@ -4310,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="N57" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="O57" t="b">
         <v>1</v>
@@ -4321,28 +4339,28 @@
         <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C58" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D58" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E58" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F58" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G58" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H58" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="I58" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
@@ -4357,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="N58" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="O58" t="b">
         <v>1</v>
@@ -4368,28 +4386,28 @@
         <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C59" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="E59" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F59" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G59" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="H59" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I59" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J59" t="b">
         <v>0</v>
@@ -4404,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="N59" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="O59" t="b">
         <v>1</v>
@@ -4415,28 +4433,28 @@
         <v>73</v>
       </c>
       <c r="B60" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="C60" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D60" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E60" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F60" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G60" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="H60" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="I60" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J60" t="b">
         <v>0</v>
@@ -4451,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="N60" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="O60" t="b">
         <v>1</v>
@@ -4462,28 +4480,28 @@
         <v>74</v>
       </c>
       <c r="B61" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D61" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E61" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F61" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G61" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H61" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I61" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
@@ -4498,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="N61" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="O61" t="b">
         <v>1</v>
@@ -4509,28 +4527,28 @@
         <v>75</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>107</v>
       </c>
       <c r="C62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D62" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E62" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F62" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G62" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="H62" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="I62" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J62" t="b">
         <v>0</v>
@@ -4545,7 +4563,7 @@
         <v>0</v>
       </c>
       <c r="N62" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="O62" t="b">
         <v>1</v>
@@ -4556,28 +4574,28 @@
         <v>76</v>
       </c>
       <c r="B63" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C63" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D63" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E63" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F63" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G63" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H63" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I63" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J63" t="b">
         <v>0</v>
@@ -4592,7 +4610,7 @@
         <v>0</v>
       </c>
       <c r="N63" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="O63" t="b">
         <v>1</v>
@@ -4603,28 +4621,28 @@
         <v>77</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D64" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E64" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F64" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G64" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="H64" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="I64" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
@@ -4639,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="N64" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="O64" t="b">
         <v>1</v>
@@ -4650,28 +4668,28 @@
         <v>78</v>
       </c>
       <c r="B65" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="D65" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E65" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F65" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G65" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="H65" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="I65" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J65" t="b">
         <v>0</v>
@@ -4686,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="N65" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="O65" t="b">
         <v>1</v>
@@ -4697,28 +4715,28 @@
         <v>79</v>
       </c>
       <c r="B66" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C66" t="s">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="D66" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E66" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F66" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G66" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="H66" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I66" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="J66" t="b">
         <v>0</v>
@@ -4733,7 +4751,7 @@
         <v>0</v>
       </c>
       <c r="N66" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="O66" t="b">
         <v>1</v>
@@ -4744,28 +4762,28 @@
         <v>80</v>
       </c>
       <c r="B67" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D67" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E67" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F67" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G67" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H67" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="I67" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J67" t="b">
         <v>0</v>
@@ -4780,7 +4798,7 @@
         <v>0</v>
       </c>
       <c r="N67" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="O67" t="b">
         <v>1</v>
@@ -4791,28 +4809,28 @@
         <v>81</v>
       </c>
       <c r="B68" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C68" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="D68" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E68" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F68" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G68" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="H68" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I68" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="J68" t="b">
         <v>0</v>
@@ -4827,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="N68" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="O68" t="b">
         <v>1</v>
@@ -4838,28 +4856,28 @@
         <v>82</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C69" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D69" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="E69" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F69" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="G69" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H69" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I69" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J69" t="b">
         <v>0</v>
@@ -4874,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="O69" t="b">
         <v>1</v>
